--- a/business_forms/046_facility_management_innovation_application--business_forms.xlsx
+++ b/business_forms/046_facility_management_innovation_application--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -926,8 +926,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -989,12 +989,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Staff'}</t>
+          <t>Staff</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'vendors'}</t>
+          <t>vendors</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Vendors'}</t>
+          <t>Vendors</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'innovators'}</t>
+          <t>innovators</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Innovators'}</t>
+          <t>Innovators</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'operational'}</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Operational'}</t>
+          <t>Operational</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'product'}</t>
+          <t>product</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Product'}</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'process'}</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Process'}</t>
+          <t>Process</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
